--- a/research/iterations/a01-bootstrap/qualified-results.xlsx
+++ b/research/iterations/a01-bootstrap/qualified-results.xlsx
@@ -1357,13 +1357,13 @@
         <v>1</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="U2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <v>30</v>
@@ -1425,13 +1425,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="U3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>30</v>
